--- a/tests/testdata/excel/ファイル名/とても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイル.xlsx
+++ b/tests/testdata/excel/ファイル名/とても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイル.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F85AA856-037E-4B18-8B9B-AF20AFF4A0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AA753E1-F1E1-4308-8C69-DCE450D40694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{506AF0B6-8A7F-465E-9AAE-D4DF3A54B32B}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{B937BA11-3760-4CC3-AC9D-5A190D9FD9C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B726BB5-41B3-45A1-869F-4589170A87BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150C653B-6233-413E-BEC5-73961021191B}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/とても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイル.xlsx
+++ b/tests/testdata/excel/ファイル名/とても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイルとても長い名前のファイル.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AA753E1-F1E1-4308-8C69-DCE450D40694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEF3DF8F-7A3E-4C77-B0B2-42ADF982A0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{B937BA11-3760-4CC3-AC9D-5A190D9FD9C2}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{E787DF96-2130-4B79-B617-23B20DE2D472}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150C653B-6233-413E-BEC5-73961021191B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717A82CE-AF2D-404E-8C4C-AF2AE0715B06}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
